--- a/AAII_Financials/Quarterly/RIO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RIO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="92">
   <si>
     <t>RIO</t>
   </si>
@@ -656,18 +656,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AE102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="13" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="15" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
@@ -676,234 +674,248 @@
     <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43465</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43281</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43100</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>42916</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>42735</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>42551</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>42369</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>42185</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>42004</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>15514000</v>
+      </c>
+      <c r="E8" s="3">
+        <v>15514000</v>
+      </c>
+      <c r="F8" s="3">
         <v>15382500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>15382500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>13436500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>13436500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>13428000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>13428000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>13401000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>13401000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>13687000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>13687000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>13333500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>13333500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>12889500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>25249000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>19362000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>22443000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>20722000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>20608000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>19914000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>20711000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>19319000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>18281000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>15500000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>16849000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>17980000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>23327000</v>
       </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>10715500</v>
+      </c>
+      <c r="E9" s="3">
+        <v>10715500</v>
+      </c>
+      <c r="F9" s="3">
         <v>10989000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>10989000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>9725000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>9725000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>9691500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>9691500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>9048000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>9048000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>9604000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>9604000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>8767500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>8767500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>8526500</v>
-      </c>
-      <c r="Q9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R9" s="3" t="s">
-        <v>5</v>
       </c>
       <c r="S9" s="3" t="s">
         <v>5</v>
@@ -938,55 +950,61 @@
       <c r="AC9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>4798500</v>
+      </c>
+      <c r="E10" s="3">
+        <v>4798500</v>
+      </c>
+      <c r="F10" s="3">
         <v>4393500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>4393500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>3711500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>3711500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>3736500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>3736500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>4353000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>4353000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>4083000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>4083000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>4566000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>4566000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>4363000</v>
-      </c>
-      <c r="Q10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R10" s="3" t="s">
-        <v>5</v>
       </c>
       <c r="S10" s="3" t="s">
         <v>5</v>
@@ -1021,8 +1039,14 @@
       <c r="AC10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1052,91 +1076,99 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F12" s="3">
         <v>262000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>262000</v>
       </c>
-      <c r="F12" s="3" t="s">
+      <c r="H12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G12" s="3" t="s">
+      <c r="I12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>199000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>199000</v>
       </c>
-      <c r="J12" s="3" t="s">
+      <c r="L12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K12" s="3" t="s">
+      <c r="M12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>122500</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>122500</v>
       </c>
-      <c r="N12" s="3" t="s">
+      <c r="P12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O12" s="3" t="s">
+      <c r="Q12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>38000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>345000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>280000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>337000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>287000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>256000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="X12" s="3">
         <v>232000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="Y12" s="3">
         <v>270000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Z12" s="3">
         <v>175000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="AA12" s="3">
         <v>230000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AB12" s="3">
         <v>267000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AC12" s="3">
         <v>333000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AD12" s="3">
         <v>243000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AE12" s="3">
         <v>407000</v>
       </c>
     </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1218,150 +1250,162 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-9500</v>
+      </c>
+      <c r="E14" s="3">
+        <v>-9500</v>
+      </c>
+      <c r="F14" s="3">
         <v>109500</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>109500</v>
       </c>
-      <c r="F14" s="3">
+      <c r="H14" s="3">
         <v>61000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="I14" s="3">
         <v>61000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="J14" s="3">
         <v>-336500</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>-336500</v>
       </c>
-      <c r="J14" s="3">
+      <c r="L14" s="3">
         <v>-20500</v>
       </c>
-      <c r="K14" s="3">
+      <c r="M14" s="3">
         <v>-20500</v>
       </c>
-      <c r="L14" s="3">
+      <c r="N14" s="3">
         <v>-50000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="O14" s="3">
         <v>-50000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="P14" s="3">
         <v>587500</v>
       </c>
-      <c r="O14" s="3">
+      <c r="Q14" s="3">
         <v>587500</v>
       </c>
-      <c r="P14" s="3">
+      <c r="R14" s="3">
         <v>153500</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="S14" s="3">
         <v>109000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="T14" s="3">
         <v>1134000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="U14" s="3">
         <v>1429000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="V14" s="3">
         <v>2349000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="W14" s="3">
         <v>-4437000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="X14" s="3">
         <v>41000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="Y14" s="3">
         <v>-1918000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Z14" s="3">
         <v>626000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="AA14" s="3">
         <v>205000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AB14" s="3">
         <v>-147000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AC14" s="3">
         <v>2311000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AD14" s="3">
         <v>416000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AE14" s="3">
         <v>-468000</v>
       </c>
     </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1806500</v>
+      </c>
+      <c r="E15" s="3">
+        <v>1806500</v>
+      </c>
+      <c r="F15" s="3">
         <v>1403000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>1403000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>1479000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>1479000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>19000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>19000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>1410500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>1410500</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>-69500</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>-69500</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>1242500</v>
       </c>
-      <c r="O15" s="3">
+      <c r="Q15" s="3">
         <v>1242500</v>
       </c>
-      <c r="P15" s="3">
+      <c r="R15" s="3">
         <v>-75000</v>
-      </c>
-      <c r="Q15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R15" s="3" t="s">
-        <v>5</v>
       </c>
       <c r="S15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T15" s="3">
-        <v>114000</v>
+      <c r="T15" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="U15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V15" s="3" t="s">
-        <v>5</v>
+      <c r="V15" s="3">
+        <v>114000</v>
       </c>
       <c r="W15" s="3" t="s">
         <v>5</v>
@@ -1375,17 +1419,23 @@
       <c r="Z15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA15" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB15" s="3">
-        <v>0</v>
+      <c r="AA15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB15" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AC15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1412,174 +1462,188 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>11162500</v>
+      </c>
+      <c r="E17" s="3">
+        <v>11162500</v>
+      </c>
+      <c r="F17" s="3">
         <v>11488000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>11488000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>10070500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>10070500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>10292000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>10292000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>9542000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>9542000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>10184500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>10184500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>9402500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>9402500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>9591000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>14490000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>13631000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>16253000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>15446000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>9379000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>13550000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>12699000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>13452000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>13719000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>13591000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>16552000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>14662000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>16975000</v>
       </c>
     </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>4351500</v>
+      </c>
+      <c r="E18" s="3">
+        <v>4351500</v>
+      </c>
+      <c r="F18" s="3">
         <v>3894500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>3894500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>3366000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>3366000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>3136000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>3136000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>3859000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>3859000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>3502500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>3502500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>3931000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>3931000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>3298500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>10759000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>5731000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>6190000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>5276000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>11229000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>6364000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>8012000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>5867000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>4562000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>1909000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>297000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>3318000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>6352000</v>
       </c>
     </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1609,423 +1673,455 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-413500</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-413500</v>
+      </c>
+      <c r="F20" s="3">
         <v>-472000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>-472000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>-211500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>-211500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>-597000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-597000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-232500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-232500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-217500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-217500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>-267000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>-267000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>-181000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>-548000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>-283000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>24000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>183000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>426000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>509000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>101000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>-818000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>-241000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>224000</v>
-      </c>
-      <c r="AA20" s="3">
-        <v>-2685000</v>
-      </c>
-      <c r="AB20" s="3">
-        <v>-1402000</v>
       </c>
       <c r="AC20" s="3">
         <v>-2685000</v>
       </c>
-    </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD20" s="3">
+        <v>-1402000</v>
+      </c>
+      <c r="AE20" s="3">
+        <v>-2685000</v>
+      </c>
+    </row>
+    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>6571500</v>
+      </c>
+      <c r="E21" s="3">
+        <v>6571500</v>
+      </c>
+      <c r="F21" s="3">
         <v>5769500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>5769500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>5056500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>5056500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>3752000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>3752000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>5502000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>5502000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>3650500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>3650500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>5440500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>5440500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>3404500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>12398000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>7540000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>8502000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>7555000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>13621000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>8922000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>10371000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>7166000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>6832000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>4416000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>-50000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>4223000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>6269000</v>
       </c>
     </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>214500</v>
+      </c>
+      <c r="E22" s="3">
+        <v>214500</v>
+      </c>
+      <c r="F22" s="3">
         <v>253500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>253500</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>272000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>272000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>195500</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>195500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>190500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>190500</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>222000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>222000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>268000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>268000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>145500</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>99000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>169000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>281000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>273000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>220000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>141000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="3">
         <v>253000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Z22" s="3">
         <v>93000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AA22" s="3">
         <v>76000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AB22" s="3">
         <v>35000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AC22" s="3">
         <v>83000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AD22" s="3">
         <v>171000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AE22" s="3">
         <v>207000</v>
       </c>
     </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>4656500</v>
+      </c>
+      <c r="E23" s="3">
+        <v>4656500</v>
+      </c>
+      <c r="F23" s="3">
         <v>3915500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>3915500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>3368500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>3368500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>3750000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>3750000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>4057500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>4057500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>3427500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>3427500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>3465000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>3465000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>3173500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>10112000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>5279000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>5933000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>5186000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>11435000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>6732000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>7860000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>4956000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>4245000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>2098000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>-2471000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>1745000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>3460000</v>
       </c>
     </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1059500</v>
+      </c>
+      <c r="E24" s="3">
+        <v>1059500</v>
+      </c>
+      <c r="F24" s="3">
         <v>1059000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>1059000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>1100500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>1100500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>908000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>908000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>1112500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>1112500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>924500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>924500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>991500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>991500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>1373500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>3163000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>1828000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>1892000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>2255000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>2009000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>2233000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>1857000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>1669000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>1210000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>357000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>47000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>946000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>1246000</v>
       </c>
     </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2107,174 +2203,192 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>3597000</v>
+      </c>
+      <c r="E26" s="3">
+        <v>3597000</v>
+      </c>
+      <c r="F26" s="3">
         <v>2856500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>2856500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>2268000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>2268000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>2842000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>2842000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>2945000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>2945000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>2503000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>2503000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>2473500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>2473500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>1800000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>6949000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>3451000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>4041000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>2931000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>9426000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>4499000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>6003000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>3287000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>3035000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>1741000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>-2518000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>799000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>2214000</v>
       </c>
     </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>3332000</v>
+      </c>
+      <c r="E27" s="3">
+        <v>3332000</v>
+      </c>
+      <c r="F27" s="3">
         <v>2719000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>2719000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>2264000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>2264000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>2872000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>2872000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>2904000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>2904000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>2470500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>2470500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>2558500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>2558500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>1724500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>6453000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>3316000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>3880000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>4130000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>9258000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>4380000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>5896000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>3305000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>2904000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>1713000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>-1672000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>806000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>2125000</v>
       </c>
     </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2356,8 +2470,14 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2400,11 +2520,11 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-      <c r="Q29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R29" s="3" t="s">
-        <v>5</v>
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3">
+        <v>0</v>
       </c>
       <c r="S29" s="3" t="s">
         <v>5</v>
@@ -2412,20 +2532,20 @@
       <c r="T29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U29" s="3">
-        <v>0</v>
+      <c r="U29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>5</v>
       </c>
       <c r="W29" s="3">
-        <v>-439000</v>
+        <v>0</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y29" s="3" t="s">
-        <v>5</v>
+      <c r="Y29" s="3">
+        <v>-439000</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>5</v>
@@ -2436,11 +2556,17 @@
       <c r="AB29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC29" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AC29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2522,8 +2648,14 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2605,174 +2737,192 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>413500</v>
+      </c>
+      <c r="E32" s="3">
+        <v>413500</v>
+      </c>
+      <c r="F32" s="3">
         <v>472000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>472000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>211500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>211500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>597000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>597000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>232500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>232500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>217500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>217500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>267000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>267000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>181000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>548000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>283000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>-24000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>-183000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>-426000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>-509000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>-101000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>818000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>241000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>-224000</v>
-      </c>
-      <c r="AA32" s="3">
-        <v>2685000</v>
-      </c>
-      <c r="AB32" s="3">
-        <v>1402000</v>
       </c>
       <c r="AC32" s="3">
         <v>2685000</v>
       </c>
-    </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD32" s="3">
+        <v>1402000</v>
+      </c>
+      <c r="AE32" s="3">
+        <v>2685000</v>
+      </c>
+    </row>
+    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>3332000</v>
+      </c>
+      <c r="E33" s="3">
+        <v>3332000</v>
+      </c>
+      <c r="F33" s="3">
         <v>2719000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>2719000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>2264000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>2264000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>2872000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>2872000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>2904000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>2904000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>2470500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>2470500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>2558500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>2558500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>1724500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>6453000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>3316000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>3880000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>4130000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>9258000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>4380000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>5457000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>3305000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>2904000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>1713000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>-1672000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>806000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>2125000</v>
       </c>
     </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2854,179 +3004,197 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>3332000</v>
+      </c>
+      <c r="E35" s="3">
+        <v>3332000</v>
+      </c>
+      <c r="F35" s="3">
         <v>2719000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>2719000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>2264000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>2264000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>2872000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>2872000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>2904000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>2904000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>2470500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>2470500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>2558500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>2558500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>1724500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>6453000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>3316000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>3880000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>4130000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>9258000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>4380000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>5457000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>3305000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>2904000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>1713000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>-1672000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>806000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>2125000</v>
       </c>
     </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43465</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43281</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43100</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>42916</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>42735</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>42551</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>42369</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>42185</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>42004</v>
       </c>
     </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3056,8 +3224,10 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3087,388 +3257,414 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>8913000</v>
+      </c>
+      <c r="E41" s="3">
+        <v>8913000</v>
+      </c>
+      <c r="F41" s="3">
         <v>8872000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>8872000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>9015000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>9015000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>8495000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>8495000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>9256000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>9256000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>9673000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>9673000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>9179000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>9179000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>6775000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>10381000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>6269000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>8027000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>6861000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>10773000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>5989000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>10550000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>7746000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>8201000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>8250000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>9366000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>11163000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>12423000</v>
       </c>
     </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>594000</v>
+      </c>
+      <c r="E42" s="3">
+        <v>594000</v>
+      </c>
+      <c r="F42" s="3">
         <v>548000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>548000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>319000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>319000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>370000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>370000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>569000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>569000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>1078000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>1078000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>1327000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>1327000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>2132000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>2851000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="T42" s="3">
         <v>2683000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="U42" s="3">
         <v>2670000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="V42" s="3">
         <v>2759000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="W42" s="3">
         <v>2692000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="X42" s="3">
         <v>2146000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="Y42" s="3">
         <v>1084000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Z42" s="3">
         <v>353000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="AA42" s="3">
         <v>359000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AB42" s="3">
         <v>134000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AC42" s="3">
         <v>223000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AD42" s="3">
         <v>387000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AE42" s="3">
         <v>417000</v>
       </c>
     </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>4888000</v>
+      </c>
+      <c r="E43" s="3">
+        <v>4888000</v>
+      </c>
+      <c r="F43" s="3">
         <v>4264000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>4264000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>4794000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>4794000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>3521000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>3521000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>4080000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>4080000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>3471000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>3471000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>3849000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>3849000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>3370000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>3706000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>2581000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>3143000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>3275000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>3256000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>2925000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>3572000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>2975000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>3558000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>2071000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>2504000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>2799000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>3623000</v>
       </c>
     </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>7733000</v>
+      </c>
+      <c r="E44" s="3">
+        <v>7733000</v>
+      </c>
+      <c r="F44" s="3">
         <v>6968000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>6968000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>6831000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>6831000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>5860000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>5860000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>6517000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>6517000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>6659000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>6659000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>6423000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>6423000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>6213000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>3917000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>3620000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>3463000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>3584000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>3447000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>3543000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>3472000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>3331000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>2937000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>3129000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>3168000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>3924000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>4350000</v>
       </c>
     </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F45" s="3">
         <v>26000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>26000</v>
       </c>
-      <c r="F45" s="3" t="s">
+      <c r="H45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G45" s="3" t="s">
+      <c r="I45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>49000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>49000</v>
       </c>
-      <c r="J45" s="3" t="s">
+      <c r="L45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K45" s="3" t="s">
+      <c r="M45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>40000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>40000</v>
       </c>
-      <c r="N45" s="3" t="s">
+      <c r="P45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O45" s="3" t="s">
+      <c r="Q45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>28000</v>
       </c>
-      <c r="Q45" s="3">
-        <v>0</v>
-      </c>
-      <c r="R45" s="3">
-        <v>0</v>
-      </c>
       <c r="S45" s="3">
         <v>0</v>
       </c>
@@ -3502,340 +3698,370 @@
       <c r="AC45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>22128000</v>
+      </c>
+      <c r="E46" s="3">
+        <v>22128000</v>
+      </c>
+      <c r="F46" s="3">
         <v>21569000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>21569000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>20959000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>20959000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>19120000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>19120000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>20422000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>20422000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>21510000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>21510000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>20778000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>20778000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>18973000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>20855000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>15153000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>17303000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>16479000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>20168000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>14603000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>18678000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>14405000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>15055000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>13584000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>15261000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>18273000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>20813000</v>
       </c>
     </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>6273000</v>
+      </c>
+      <c r="E47" s="3">
+        <v>6273000</v>
+      </c>
+      <c r="F47" s="3">
         <v>6484000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>6484000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>5436000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>5436000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>5355000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>5355000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>5026000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>5026000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>4787000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>4787000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>3574000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>3574000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>3663000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>6393000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>6869000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>6327000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>6666000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>6706000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>6832000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>6750000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>7070000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AA47" s="3">
         <v>7221000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AB47" s="3">
         <v>7578000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AC47" s="3">
         <v>7163000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AD47" s="3">
         <v>7227000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AE47" s="3">
         <v>6964000</v>
       </c>
     </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>88031000</v>
+      </c>
+      <c r="E48" s="3">
+        <v>88031000</v>
+      </c>
+      <c r="F48" s="3">
         <v>84310000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>84310000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>79131000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>79131000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>68573000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>68573000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>66579000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>66579000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>66468000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>66468000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>63101000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>63101000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>64734000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>62882000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>55836000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>57372000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>56349000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>56361000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>57742000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>62093000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>60324000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>58855000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>60967000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>61057000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>65410000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>68693000</v>
       </c>
     </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>8096000</v>
+      </c>
+      <c r="E49" s="3">
+        <v>8096000</v>
+      </c>
+      <c r="F49" s="3">
         <v>8176000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>8176000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>7721000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>7721000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>3531000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>3531000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>4558000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>4558000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>5186000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>5186000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>4473000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>4473000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>4471000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>3701000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>3323000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>3559000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>3564000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>3691000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>3953000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>4156000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>3987000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>4230000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>4349000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>4228000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>6730000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>7108000</v>
       </c>
     </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3917,8 +4143,14 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4000,91 +4232,103 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>4432000</v>
+      </c>
+      <c r="E52" s="3">
+        <v>4432000</v>
+      </c>
+      <c r="F52" s="3">
         <v>2475000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>2475000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>3587000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>3587000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>1682000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>1682000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>1867000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>1867000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>1974000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>1974000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>2545000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>2545000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>2137000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>3559000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>3348000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>3241000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>3694000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>4023000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>6461000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>4049000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>5065000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>3902000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>3910000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>3855000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>3663000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>4249000</v>
       </c>
     </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4166,91 +4410,103 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>133500000</v>
+      </c>
+      <c r="E54" s="3">
+        <v>133500000</v>
+      </c>
+      <c r="F54" s="3">
         <v>128102000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>128102000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>120805000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>120805000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>102786000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>102786000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>101887000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>101887000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>103549000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>103549000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>97556000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>97556000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>96774000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>97390000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>84529000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>87802000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>86752000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>90949000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>89591000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>95726000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>90851000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>89263000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>90388000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>91564000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>101303000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>107827000</v>
       </c>
     </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4280,8 +4536,10 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4311,506 +4569,544 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>9706000</v>
+      </c>
+      <c r="E57" s="3">
+        <v>9706000</v>
+      </c>
+      <c r="F57" s="3">
         <v>3596000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>3596000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>9233000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>9233000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>3196000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>3196000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>7689000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>7689000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>3275000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>3275000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>7630000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>7630000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>3367000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>7421000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>6194000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>6480000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>6380000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>6600000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>6406000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>7061000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>5964000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>6361000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>5557000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>6237000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>6032000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>7437000</v>
       </c>
     </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1730000</v>
+      </c>
+      <c r="E58" s="3">
+        <v>1730000</v>
+      </c>
+      <c r="F58" s="3">
         <v>1257000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>1257000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>875000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>875000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>562000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>562000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>1099000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>1099000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>1370000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>1370000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>474000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>474000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>1215000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>584000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>588000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>1022000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>1102000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>311000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>428000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>904000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>742000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>922000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>1068000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>2484000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>4422000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>2684000</v>
       </c>
     </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>3634000</v>
+      </c>
+      <c r="E59" s="3">
+        <v>3634000</v>
+      </c>
+      <c r="F59" s="3">
         <v>4982000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>4982000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>3204000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>3204000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>4333000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>4333000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>2884000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>2884000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>4175000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>4175000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>1990000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>1990000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>3535000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>3602000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>2618000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>3623000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>3415000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>3659000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>3123000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>3260000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>2400000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>2079000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>1430000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>1325000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>1526000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>2099000</v>
       </c>
     </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>15542000</v>
+      </c>
+      <c r="E60" s="3">
+        <v>15542000</v>
+      </c>
+      <c r="F60" s="3">
         <v>14930000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>14930000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>13739000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>13739000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>11743000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>11743000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>12034000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>12034000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>12743000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>12743000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>10446000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>10446000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>11603000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>11607000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>9400000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>11125000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>10897000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>10570000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>9957000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>11225000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>9106000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>9362000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>8055000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>10046000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>11980000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>12220000</v>
       </c>
     </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>21122000</v>
+      </c>
+      <c r="E61" s="3">
+        <v>21122000</v>
+      </c>
+      <c r="F61" s="3">
         <v>22491000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>22491000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>22765000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>22765000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>13660000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>13660000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>13200000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>13200000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>13498000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>13498000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>13604000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>13604000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>11056000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>13247000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>13191000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>13093000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>13062000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>12440000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>12485000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>15148000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>15106000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>17470000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>20799000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>21140000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>20943000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>22535000</v>
       </c>
     </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>19675000</v>
+      </c>
+      <c r="E62" s="3">
+        <v>19675000</v>
+      </c>
+      <c r="F62" s="3">
         <v>18145000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>18145000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>17094000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>17094000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>15568000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>15568000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>15966000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>15966000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>18280000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>18280000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>15725000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>15725000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>18096000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>20633000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>18282000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>18342000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>18493000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>18115000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>18533000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>18238000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>17814000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>16701000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>17474000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>16250000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>17747000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>18478000</v>
       </c>
     </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4892,8 +5188,14 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4975,8 +5277,14 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5058,91 +5366,103 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>61800000</v>
+      </c>
+      <c r="E66" s="3">
+        <v>61800000</v>
+      </c>
+      <c r="F66" s="3">
         <v>61078000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>61078000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>58838000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>58838000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>44821000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>44821000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>44723000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>44723000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>47208000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>47208000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>44199000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>44199000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>44033000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>50336000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>45305000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>47270000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>47187000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>47262000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>47258000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>51015000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>48560000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>49973000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>52895000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>54215000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>58656000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>61542000</v>
       </c>
     </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5172,8 +5492,10 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+      <c r="AE67" s="3"/>
+    </row>
+    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5255,8 +5577,14 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5338,8 +5666,14 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5421,8 +5755,14 @@
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5504,91 +5844,103 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>49287000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>49287000</v>
+      </c>
+      <c r="F72" s="3">
         <v>46581000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>46581000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>43377000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>43377000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>42539000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>42539000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>40149000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>40149000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>38350000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>38350000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>36430000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>36430000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>35020000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>38752000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>31330000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>32564000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>31597000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>35686000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>33897000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>36045000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>33605000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>30847000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>28938000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>28875000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>33954000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>37232000</v>
       </c>
     </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5670,8 +6022,14 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5753,8 +6111,14 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5836,91 +6200,103 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>65461000</v>
+      </c>
+      <c r="E76" s="3">
+        <v>65461000</v>
+      </c>
+      <c r="F76" s="3">
         <v>62203000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>62203000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>58203000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>58203000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>55246000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>55246000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>55253000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>55253000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>54586000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>54586000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>51625000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>51625000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>50634000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>47054000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>39224000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>40532000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>39565000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>43686000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>42333000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>44711000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>42291000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>39290000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>37493000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>37349000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>42647000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>46285000</v>
       </c>
     </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6002,179 +6378,197 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43465</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43281</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43100</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>42916</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>42735</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>42551</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>42369</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>42185</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>42004</v>
       </c>
     </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>3332000</v>
+      </c>
+      <c r="E81" s="3">
+        <v>3332000</v>
+      </c>
+      <c r="F81" s="3">
         <v>2719000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>2719000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>2264000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>2264000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>2872000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>2872000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>2904000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>2904000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>2470500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>2470500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>2558500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>2558500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>1724500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>6453000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>3316000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>3880000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>4130000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>9258000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>4380000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>5457000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>3305000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>2904000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>1713000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>-1672000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>806000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>2125000</v>
       </c>
     </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6204,91 +6598,99 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+      <c r="AE82" s="3"/>
+    </row>
+    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1479000</v>
+      </c>
+      <c r="E83" s="3">
+        <v>1479000</v>
+      </c>
+      <c r="F83" s="3">
         <v>1274000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>1274000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>1410500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>1410500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>1155000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>1247000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>1242500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>1242500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>1077500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>1077500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>1229500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>1229500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>1093500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>2187000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>2092000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>2288000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>2096000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>1966000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>2049000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>2258000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>2117000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>2511000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>2283000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>2338000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AD83" s="3">
         <v>2307000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AE83" s="3">
         <v>2602000</v>
       </c>
     </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6370,8 +6772,14 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6453,8 +6861,14 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6536,8 +6950,14 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6619,8 +7039,14 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6702,91 +7128,103 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>4586500</v>
+      </c>
+      <c r="E89" s="3">
+        <v>4586500</v>
+      </c>
+      <c r="F89" s="3">
         <v>4954000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>4954000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>3462000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>3462000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>4271500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>4271500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>3528000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>3528000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>4092500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>4092500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>3487500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>3487500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>2830000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>10247000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>5628000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>8523000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>6389000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>6593000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>5228000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>7578000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>6306000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>5225000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>3240000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>4948000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>4435000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>8830000</v>
       </c>
     </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6816,91 +7254,99 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+      <c r="AE90" s="3"/>
+    </row>
+    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2973500</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-2973500</v>
+      </c>
+      <c r="F91" s="3">
         <v>-3800500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-3800500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-2367000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-2367000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-2801500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-2801500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-2009000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-2009000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-2042500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-2042500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-1500500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-1500500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-1802000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-3496000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-2693000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-3097000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-2391000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-3067000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-2363000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-2724000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-1758000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-1694000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-1318000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-2211000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-2474000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-4317000</v>
       </c>
     </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6982,8 +7428,14 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7065,91 +7517,103 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2725000</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-2725000</v>
+      </c>
+      <c r="F94" s="3">
         <v>-4056500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-4056500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-5611000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-5611000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-3025000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-3025000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-1772000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-1772000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-2363000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-2363000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-1118000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-1118000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-1342500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-3621000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-2935000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-3126000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-2375000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>4323000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-3002000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-846000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-1527000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-1467000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-637000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-2182000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-2418000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-3787000</v>
       </c>
     </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7179,91 +7643,99 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+      <c r="AE95" s="3"/>
+    </row>
+    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>2105500</v>
+      </c>
+      <c r="E96" s="3">
+        <v>2105500</v>
+      </c>
+      <c r="F96" s="3">
         <v>1191500</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>1191500</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>1881000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>1881000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3">
         <v>1452000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>1452000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>2060500</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>2060500</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>1389500</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>1389500</v>
       </c>
-      <c r="N96" s="3">
+      <c r="P96" s="3">
         <v>1845500</v>
       </c>
-      <c r="O96" s="3">
+      <c r="Q96" s="3">
         <v>1845500</v>
       </c>
-      <c r="P96" s="3">
+      <c r="R96" s="3">
         <v>2065500</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="S96" s="3">
         <v>-2525000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="T96" s="3">
         <v>-3607000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="U96" s="3">
         <v>-3491000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="V96" s="3">
         <v>-6843000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="W96" s="3">
         <v>-2179000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="X96" s="3">
         <v>-3177000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="Y96" s="3">
         <v>-2002000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Z96" s="3">
         <v>-2248000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="AA96" s="3">
         <v>-809000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AB96" s="3">
         <v>-1916000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AC96" s="3">
         <v>-1914000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AD96" s="3">
         <v>-2162000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AE96" s="3">
         <v>-1704000</v>
       </c>
     </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7345,8 +7817,14 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7428,8 +7906,14 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7511,253 +7995,277 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1825500</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-1825500</v>
+      </c>
+      <c r="F100" s="3">
         <v>-965500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-965500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>2360000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>2360000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-1596500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-1596500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-1950500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-1950500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-1498500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-1498500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-1140000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-1140000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-3825500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-2685000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-4445000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-4338000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-7881000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-6192000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-6759000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-3986000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>-5155000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>-3767000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>-3724000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-4503000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>-3167000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>-2069000</v>
       </c>
     </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>53500</v>
+      </c>
+      <c r="E101" s="3">
+        <v>53500</v>
+      </c>
+      <c r="F101" s="3">
         <v>-34500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-34500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>-15000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-15000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>18000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>18000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-29500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-29500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>20500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>20500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>-13000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>-13000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>60500</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>186000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>-21000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>-20000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>-34000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>171000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>-20000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="Y101" s="3">
         <v>15000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Z101" s="3">
         <v>-27000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="AA101" s="3">
         <v>-36000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AB101" s="3">
         <v>1000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AC101" s="3">
         <v>-69000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AD101" s="3">
         <v>-90000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AE101" s="3">
         <v>-150000</v>
       </c>
     </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>24000</v>
+      </c>
+      <c r="E102" s="3">
+        <v>24000</v>
+      </c>
+      <c r="F102" s="3">
         <v>-74000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-74000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>264500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>264500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-384500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-384500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-209500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-209500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>249000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>249000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>1200000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>1200000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-2317500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>4127000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-1773000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>1039000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-3901000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>4895000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-4553000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>2761000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>-403000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>-45000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-1120000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>-1806000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>-1240000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>2824000</v>
       </c>
     </row>
